--- a/artfynd/A 20396-2022 artfynd.xlsx
+++ b/artfynd/A 20396-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 20396-2022 artfynd.xlsx
+++ b/artfynd/A 20396-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,49 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101775819</v>
+        <v>101774450</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -726,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567890.146411219</v>
+        <v>567869</v>
       </c>
       <c r="R2" t="n">
-        <v>6676825.326947801</v>
+        <v>6676977</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,7 +747,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -771,7 +757,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,68 +772,64 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101775508</v>
+        <v>101774746</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567931.7906619203</v>
+        <v>567863</v>
       </c>
       <c r="R3" t="n">
-        <v>6676834.54900873</v>
+        <v>6676843</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +871,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Mat hål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,69 +891,72 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101774746</v>
+        <v>101774529</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220093</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567863.9375606392</v>
+        <v>567868</v>
       </c>
       <c r="R4" t="n">
-        <v>6676842.731599597</v>
+        <v>6676948</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -998,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Mat hål</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,64 +1013,59 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101775559</v>
+        <v>101774542</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1095,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567920.9165920488</v>
+        <v>567847</v>
       </c>
       <c r="R5" t="n">
-        <v>6676830.371183628</v>
+        <v>6676957</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1130,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,15 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>101779914</v>
+        <v>101774950</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,21 +1175,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1222,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567971.7663531044</v>
+        <v>567968</v>
       </c>
       <c r="R6" t="n">
-        <v>6676853.183049097</v>
+        <v>6676831</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1257,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1267,7 +1229,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,27 +1244,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>101775856</v>
+        <v>101775241</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,16 +1284,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1345,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567863.1820311426</v>
+        <v>567955</v>
       </c>
       <c r="R7" t="n">
-        <v>6676829.796184054</v>
+        <v>6676832</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1380,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1390,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,66 +1353,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>101774542</v>
+        <v>101775339</v>
       </c>
       <c r="B8" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1472,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567847.3860201587</v>
+        <v>567961</v>
       </c>
       <c r="R8" t="n">
-        <v>6676956.727084515</v>
+        <v>6676840</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1507,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1517,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1532,27 +1471,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>101775564</v>
+        <v>101775508</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,12 +1513,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1595,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567920.0505219861</v>
+        <v>567932</v>
       </c>
       <c r="R9" t="n">
-        <v>6676823.397400577</v>
+        <v>6676835</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1630,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1640,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1655,27 +1584,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>101775565</v>
+        <v>101775512</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1624,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1709,10 +1642,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567925.7637084418</v>
+        <v>567928</v>
       </c>
       <c r="R10" t="n">
-        <v>6676837.41890596</v>
+        <v>6676841</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1744,7 +1677,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1754,7 +1687,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1769,27 +1702,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>101779916</v>
+        <v>101775559</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1744,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1826,7 +1754,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1836,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567972.6507871181</v>
+        <v>567921</v>
       </c>
       <c r="R11" t="n">
-        <v>6676859.163185491</v>
+        <v>6676830</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1871,7 +1799,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1881,7 +1809,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1896,27 +1824,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>101775890</v>
+        <v>101775564</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1866,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1959,10 +1882,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567873.0981311289</v>
+        <v>567921</v>
       </c>
       <c r="R12" t="n">
-        <v>6676805.131272291</v>
+        <v>6676823</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1994,7 +1917,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2004,7 +1927,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2019,27 +1942,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>101775738</v>
+        <v>101775565</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2064,16 +1982,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -2082,10 +1991,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567873.9455013226</v>
+        <v>567926</v>
       </c>
       <c r="R13" t="n">
-        <v>6676839.93550191</v>
+        <v>6676838</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2117,7 +2026,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2127,7 +2036,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2142,12 +2051,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2157,12 +2066,7 @@
         <v>101775684</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,10 +2100,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567898.9561973718</v>
+        <v>567899</v>
       </c>
       <c r="R14" t="n">
-        <v>6676833.442172489</v>
+        <v>6676833</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2268,15 +2172,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>101774950</v>
+        <v>101775703</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2301,7 +2200,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2310,10 +2218,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567968.1916468774</v>
+        <v>567894</v>
       </c>
       <c r="R15" t="n">
-        <v>6676831.24963467</v>
+        <v>6676843</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2345,7 +2253,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2355,7 +2263,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2385,12 +2293,7 @@
         <v>101775715</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,10 +2331,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567878.7189128834</v>
+        <v>567879</v>
       </c>
       <c r="R16" t="n">
-        <v>6676850.957572321</v>
+        <v>6676851</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2500,15 +2403,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>101775512</v>
+        <v>101775738</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2535,7 +2433,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2551,10 +2449,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567927.6988580292</v>
+        <v>567874</v>
       </c>
       <c r="R17" t="n">
-        <v>6676840.436715043</v>
+        <v>6676839</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2586,7 +2484,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2596,7 +2494,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2623,15 +2521,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>101775339</v>
+        <v>101775819</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2658,7 +2551,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2674,10 +2567,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567961.058589388</v>
+        <v>567890</v>
       </c>
       <c r="R18" t="n">
-        <v>6676840.062643005</v>
+        <v>6676825</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2709,7 +2602,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2719,7 +2612,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2734,27 +2627,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>101775703</v>
+        <v>101775856</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2781,7 +2669,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2797,10 +2685,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567893.7953871277</v>
+        <v>567863</v>
       </c>
       <c r="R19" t="n">
-        <v>6676843.285874985</v>
+        <v>6676830</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2832,7 +2720,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2842,7 +2730,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2857,49 +2745,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>101774450</v>
+        <v>101775886</v>
       </c>
       <c r="B20" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2911,10 +2794,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567869.409834059</v>
+        <v>567873</v>
       </c>
       <c r="R20" t="n">
-        <v>6676977.014183999</v>
+        <v>6676805</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2946,7 +2829,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2956,7 +2839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2983,15 +2866,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>101775241</v>
+        <v>101775949</v>
       </c>
       <c r="B21" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3016,7 +2894,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -3025,10 +2912,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>567955.2347456565</v>
+        <v>567890</v>
       </c>
       <c r="R21" t="n">
-        <v>6676832.002768238</v>
+        <v>6676798</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3060,7 +2947,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3070,7 +2957,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3085,15 +2972,368 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>101779640</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Avesta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>567974</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6676816</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Folkärna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>fanny westling</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>fanny westling</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>101779914</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Avesta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>567971</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6676853</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Folkärna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Annelie Hilmerby</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Annelie Hilmerby</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>101779916</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Avesta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>567972</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6676859</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Folkärna</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
           <t>Philipp Weiss</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
+      <c r="AX24" t="inlineStr">
         <is>
           <t>Philipp Weiss</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20396-2022 artfynd.xlsx
+++ b/artfynd/A 20396-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101774450</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101774746</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101774529</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1144,6 +1164,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101774542</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1253,6 +1278,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101774950</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1362,6 +1392,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101775241</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1480,6 +1515,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101775339</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1593,6 +1633,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101775508</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1711,6 +1756,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101775512</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1833,6 +1883,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101775559</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1951,6 +2006,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101775564</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2060,6 +2120,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101775565</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2169,6 +2234,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101775684</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2287,6 +2357,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101775703</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2400,6 +2475,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101775715</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2518,6 +2598,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101775738</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2636,6 +2721,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101775819</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2754,6 +2844,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101775856</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2863,6 +2958,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101775886</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2981,6 +3081,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101775949</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3090,6 +3195,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101779640</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3212,6 +3322,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101779914</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3334,8 +3449,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101779916</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>